--- a/results/Int All Data -0.3/Rando_6_permute.xlsx
+++ b/results/Int All Data -0.3/Rando_6_permute.xlsx
@@ -440,837 +440,837 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7407914582837184</v>
+        <v>0.7582757799476065</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7404781750756984</v>
+        <v>0.7652275485092823</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.73983176266458</v>
+        <v>0.7645811360981639</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7395383254516381</v>
+        <v>0.7627411288402001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7395383254516381</v>
+        <v>0.7614185350253462</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7429745177423196</v>
+        <v>0.7638454167091937</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7304630354165957</v>
+        <v>0.7735968881479718</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7292396715771329</v>
+        <v>0.7732836049399516</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7335561755066399</v>
+        <v>0.7742333775615509</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7443821658217943</v>
+        <v>0.7799022442985291</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7428157497816941</v>
+        <v>0.7908076185939963</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7428653647693895</v>
+        <v>0.7914341850100364</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7419155921477902</v>
+        <v>0.7948009163179441</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7391754272559226</v>
+        <v>0.8144286054502773</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.741985053130564</v>
+        <v>0.8084762244978964</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7391754272559226</v>
+        <v>0.8112461583823813</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7388720670454416</v>
+        <v>0.8112461583823813</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7381363476564715</v>
+        <v>0.805049955204754</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7371667290397941</v>
+        <v>0.8019072001270144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7371865750348723</v>
+        <v>0.8185707481373117</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7374204742625795</v>
+        <v>0.8195105977613717</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7430992639970968</v>
+        <v>0.8035728461425056</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7409516438154209</v>
+        <v>0.7960639721475635</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.740031640186439</v>
+        <v>0.7976204651901246</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7386693543814287</v>
+        <v>0.7973171049796437</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7331904421687703</v>
+        <v>0.8007532972703251</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7382327424897084</v>
+        <v>0.8054426223930868</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7401322877329068</v>
+        <v>0.7981081096406174</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7441893761553204</v>
+        <v>0.7984511618412548</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7432495265312602</v>
+        <v>0.7984511618412548</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7417228024813164</v>
+        <v>0.7948562015899477</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.74157395751823</v>
+        <v>0.7989388062917475</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.74157395751823</v>
+        <v>0.7983023168781682</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7397041812676488</v>
+        <v>0.8040108756053028</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7470684630127354</v>
+        <v>0.801976661109788</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7480083126367956</v>
+        <v>0.7994703954456277</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7454921239750961</v>
+        <v>0.8003804760770705</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7375508908016648</v>
+        <v>0.8063229340319124</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7372376075936448</v>
+        <v>0.8053037004275394</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7382667641955567</v>
+        <v>0.8046771340114993</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7385800474035769</v>
+        <v>0.8049408022318238</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7385800474035769</v>
+        <v>0.800534991324465</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7385800474035769</v>
+        <v>0.8005449143220041</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7372574535887229</v>
+        <v>0.8062832420417561</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7317034101089829</v>
+        <v>0.8044233887887139</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7329267739484457</v>
+        <v>0.8004456843466131</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7474129327844499</v>
+        <v>0.7968507240953061</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.74803949920049</v>
+        <v>0.7955182072829132</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7505159958720331</v>
+        <v>0.7871049229408362</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7540117261479491</v>
+        <v>0.7893574433822113</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7311335465360234</v>
+        <v>0.7916496558137425</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7314369067465043</v>
+        <v>0.7910528583903197</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7355294344458432</v>
+        <v>0.7904957529570533</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7256191950464397</v>
+        <v>0.7904957529570533</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7243859082094376</v>
+        <v>0.7904957529570533</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7028856076843693</v>
+        <v>0.7956670522459997</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7087288356638202</v>
+        <v>0.7944536114040758</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7061134170267297</v>
+        <v>0.7925143741707209</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7064961612175235</v>
+        <v>0.7894311570782159</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7109615101101169</v>
+        <v>0.7888045906621758</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7119112827317162</v>
+        <v>0.7888045906621758</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7100712754737523</v>
+        <v>0.7904503906825888</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7220993660622144</v>
+        <v>0.781847151816192</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7180110910761066</v>
+        <v>0.7822695879971422</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7230732373921228</v>
+        <v>0.7794301931298835</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7285578198890892</v>
+        <v>0.7819959967792784</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7375182866668935</v>
+        <v>0.7794500391249617</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7220993660622144</v>
+        <v>0.7635718254913302</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7217761598566552</v>
+        <v>0.763561902493791</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.716410653330158</v>
+        <v>0.763561902493791</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6984897197745495</v>
+        <v>0.7708921625330294</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7011745993944136</v>
+        <v>0.71733065695914</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6776556776556777</v>
+        <v>0.7195732544029758</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6776556776556777</v>
+        <v>0.7298818312750202</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.670087265675501</v>
+        <v>0.6556563921115005</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6691077240612844</v>
+        <v>0.6599728960410075</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6608872293856813</v>
+        <v>0.6492518059855521</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.643385896868869</v>
+        <v>0.6492518059855521</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6301145964458659</v>
+        <v>0.6467356173238527</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6329142993229681</v>
+        <v>0.6467356173238527</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6199903038138332</v>
+        <v>0.6329256398915841</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6124176391204255</v>
+        <v>0.6329752548792796</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.598498508715227</v>
+        <v>0.626027739030835</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.583815307499518</v>
+        <v>0.6258335317932842</v>
       </c>
     </row>
     <row r="86">
@@ -1280,707 +1280,707 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5904934848433301</v>
+        <v>0.6275190238038535</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5824133297043514</v>
+        <v>0.6275190238038535</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5842632599598544</v>
+        <v>0.6328448383401943</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5952480182356343</v>
+        <v>0.6375242404654169</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5922044931332857</v>
+        <v>0.6383988818199344</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5944754419986619</v>
+        <v>0.6383988818199344</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5935455153721407</v>
+        <v>0.6171452386622666</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5926198414588507</v>
+        <v>0.6168021864616292</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5933257918552036</v>
+        <v>0.5960262647569149</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6351852481883442</v>
+        <v>0.5281118520282607</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6563339910863131</v>
+        <v>0.5355413420428901</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6569208655121967</v>
+        <v>0.5322043797275995</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6569208655121967</v>
+        <v>0.5353272888102609</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6505162793862485</v>
+        <v>0.5412697467651028</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6498400979825129</v>
+        <v>0.5409564635570827</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6496302974631147</v>
+        <v>0.541289592760181</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.655103539391465</v>
+        <v>0.5409564635570827</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6587693781966228</v>
+        <v>0.5331541523491987</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6665518434094286</v>
+        <v>0.539439662504678</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6707138320915411</v>
+        <v>0.5384998128806178</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6597815239456106</v>
+        <v>0.5419459281688384</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6486876126969006</v>
+        <v>0.5429155467855158</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5880184057428639</v>
+        <v>0.5429155467855158</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5497850962247247</v>
+        <v>0.5429155467855158</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5416368976740493</v>
+        <v>0.5304338334524092</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5414143390149582</v>
+        <v>0.5282210050011907</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5588972431077694</v>
+        <v>0.5201351795779041</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5588972431077694</v>
+        <v>0.5201351795779041</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5619563614919652</v>
+        <v>0.5210651062044251</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5581827872849544</v>
+        <v>0.5226315222445254</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5732841719683825</v>
+        <v>0.5358744712459883</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5010801891606845</v>
+        <v>0.5378534004694995</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5010801891606845</v>
+        <v>0.5406332573515236</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4924230825933612</v>
+        <v>0.5407126413318364</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4504502205740596</v>
+        <v>0.5154954694428379</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4504502205740596</v>
+        <v>0.5157889066557797</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4366359904285601</v>
+        <v>0.5158938069154787</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4346173692148925</v>
+        <v>0.5149341112963404</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4356068338266481</v>
+        <v>0.5148192880391023</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4324073759058279</v>
+        <v>0.5147002120686331</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4886962882318919</v>
+        <v>0.5147002120686331</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4886962882318919</v>
+        <v>0.5162666281087334</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4886962882318919</v>
+        <v>0.5162467821136552</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4887359802220483</v>
+        <v>0.5056802073055943</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4887359802220483</v>
+        <v>0.5062869277265563</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4881732045044739</v>
+        <v>0.5023489152746119</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5039947152950249</v>
+        <v>0.5017223488585717</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5039947152950249</v>
+        <v>0.4945664500618061</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.498768130734075</v>
+        <v>0.4955162226834053</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5002948547840189</v>
+        <v>0.4997575953458306</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5083650869254585</v>
+        <v>0.4928667823404665</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.510070424931106</v>
+        <v>0.4893568763537804</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.513770285442112</v>
+        <v>0.4848064731965661</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5052067385658717</v>
+        <v>0.4857463228206262</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5033369623152905</v>
+        <v>0.507599598543871</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5045007881695188</v>
+        <v>0.4981770035949603</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5048438403701562</v>
+        <v>0.4807834064800009</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5048438403701562</v>
+        <v>0.4987071751777634</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5048438403701562</v>
+        <v>0.4987071751777634</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5038841447510178</v>
+        <v>0.4987071751777634</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5038841447510178</v>
+        <v>0.4993535875888817</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.504207350956577</v>
+        <v>0.4999900770024609</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.504207350956577</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5020639834881321</v>
+        <v>0.50031328320802</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5020639834881321</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5027004729017113</v>
+        <v>0.4996767937944409</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.502054060490593</v>
+        <v>0.4996767937944409</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5033171163202124</v>
+        <v>0.4996767937944409</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5030236791072704</v>
+        <v>0.4996767937944409</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5004777214529537</v>
+        <v>0.4996767937944409</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4995577178239717</v>
+        <v>0.4996767937944409</v>
       </c>
     </row>
   </sheetData>
